--- a/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,15</t>
+          <t>-0,46; 1,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,06</t>
+          <t>-0,59; 1,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,94</t>
+          <t>-0,89; 0,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 10,02</t>
+          <t>-6,27; 10,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,89; —</t>
+          <t>-75,91; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 494,92</t>
+          <t>-68,58; 514,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 38,89</t>
+          <t>-16,68; 38,75</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,95</t>
+          <t>-0,69; 0,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,35</t>
+          <t>0,02; 1,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,23</t>
+          <t>-1,24; 0,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -2,29</t>
+          <t>-13,0; -2,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 1452,09</t>
+          <t>-29,82; 1254,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,91; 48,25</t>
+          <t>-79,0; 67,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,64; -24,69</t>
+          <t>-85,94; -27,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,14</t>
+          <t>-1,5; 2,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,06</t>
+          <t>-3,76; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,77</t>
+          <t>-0,18; 4,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 6,34</t>
+          <t>-17,55; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,83; 626,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 187,04</t>
+          <t>-66,25; 213,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 1101,36</t>
+          <t>-31,18; 1210,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,15; 103,75</t>
+          <t>-71,74; 88,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,8</t>
+          <t>-0,39; 0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,99</t>
+          <t>-0,18; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,64</t>
+          <t>-0,58; 0,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,12</t>
+          <t>-11,61; 1,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 243,11</t>
+          <t>-49,16; 212,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 196,51</t>
+          <t>-18,38; 200,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 102,9</t>
+          <t>-47,31; 116,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 14,01</t>
+          <t>-61,31; 11,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,05</t>
+          <t>-0,4; 1,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,09</t>
+          <t>-0,53; 1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,92</t>
+          <t>-0,79; 0,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 10,09</t>
+          <t>-7,03; 9,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,91; —</t>
+          <t>-74,32; 982,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 514,08</t>
+          <t>-62,54; 609,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 692,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 38,75</t>
+          <t>-19,36; 38,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,78</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-59,2%</t>
+          <t>-23,67%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,82</t>
+          <t>-0,64; 0,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,23</t>
+          <t>0,06; 1,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,24</t>
+          <t>-1,28; 0,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -2,68</t>
+          <t>-6,28; 1,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 1254,26</t>
+          <t>-43,26; 1598,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 67,69</t>
+          <t>-81,06; 50,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,94; -27,14</t>
+          <t>-50,17; 17,3</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-20,27%</t>
+          <t>-21,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,26</t>
+          <t>-1,96; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,75</t>
+          <t>-4,12; 3,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,79</t>
+          <t>-0,02; 4,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 6,04</t>
+          <t>-18,37; 5,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-86,83; 626,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 213,27</t>
+          <t>-71,61; 167,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 1210,29</t>
+          <t>-33,63; 1211,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,74; 88,51</t>
+          <t>-73,8; 81,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-19,82%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,73</t>
+          <t>-0,37; 0,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,03</t>
+          <t>-0,24; 1,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,68</t>
+          <t>-0,59; 0,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 1,82</t>
+          <t>-2,66; 4,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 212,0</t>
+          <t>-45,44; 216,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 200,21</t>
+          <t>-23,77; 206,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 116,16</t>
+          <t>-45,11; 106,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 11,7</t>
+          <t>-15,01; 37,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
